--- a/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Fabrice appelle un adulte. Il dit : maman, la lumière. Maman vient. Maman allume la lampe. La pièce est claire. Papa entre. Papa dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour. Maman dit : les prises sont pour les adultes. Fabrice tient les cubes. Les mains sont avec les jouets.</t>
+          <t>Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Fabrice appelle un adulte. Maman, la lumière. Maman vient. Maman allume la lampe. La pièce est claire. Papa entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour. Les prises sont pour les adultes. Fabrice tient les cubes. Les mains sont avec les jouets.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Fabrice appelle un adulte.
+narrateur|Maman, la lumière. Maman vient. Maman allume la lampe.
+narrateur|La pièce est claire. Papa entre.
+papa|On appelle un adulte. On appelle papa ou maman.
+narrateur|Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour.
+maman|Les prises sont pour les adultes.
+narrateur|Fabrice tient les cubes. Les mains sont avec les jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Fabrice veut la lumière. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1673,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Fabrice a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1840,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Fabrice pousse un cube. La lumière reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2007,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Fabrice tient les cubes. Les mains sont avec les jouets.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Fabrice veut la lumière. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1678,6 +1685,7 @@
           <t>narrateur|Fabrice a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Fabrice pousse un cube. La lumière reste allumée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fabrice appelle pour la lumière</t>
+          <t>La tour de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le radiateur tic. Raphaël construit une tour de cubes. Il appelle maman pour la lumière. Les mains restent avec les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Fabrice appelle un adulte. Maman, la lumière. Maman vient. Maman allume la lampe. La pièce est claire. Papa entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour. Les prises sont pour les adultes. Fabrice tient les cubes. Les mains sont avec les jouets.</t>
+          <t>Le radiateur du salon fait tic tic tic. Un coussin bleu a un gros bouton. La fenêtre est un peu embuée. Derrière, on voit les toits du village. Ça sent le pain encore chaud. Raphaël, tu as vu les toits ? Oui, maman. Ils sont gris. Ils sont gris, et tout calmes. J'ai plié une serviette près de la porte. Merci. Un rayon pâle passe sur le coussin. Le bouton bleu brille un peu. Tu as vu le bouton ? Oui. Il est rond. En ce moment, Raphaël est au tapis. Le tapis a des ronds verts. Les cubes en bois sont lisses. Un cube jaune attend. Un cube rouge attend aussi. Je fais une tour, maman. Une grande tour. Raphaël pose le cube jaune. Il pose le cube rouge dessus. Le bois fait un petit toc. Tes mains sont avec les cubes ? Oui, papa. Bravo. Le salon est un peu sombre. Raphaël veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Raphaël appelle un adulte. Maman, la lumière. J'arrive, Raphaël. Maman vient près du tapis. Je m'occupe de la lumière. Maman allume la lampe. La pièce est claire. La tour jaune et rouge brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Raphaël. Les prises sont pour les adultes. Les mains restent avec les jouets. Raphaël reprend un cube. Il construit une tour plus haute. La tour est haute. Oui. Tes mains sont avec les cubes. Tu as fait du bon travail. Raphaël tient les cubes. Les mains sont avec les jouets. Le radiateur fait encore tic tic.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Fabrice appelle un adulte.
-narrateur|Maman, la lumière. Maman vient. Maman allume la lampe.
-narrateur|La pièce est claire. Papa entre.
-papa|On appelle un adulte. On appelle papa ou maman.
-narrateur|Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour.
+          <t>narrateur|Le radiateur du salon fait tic tic tic.
+narrateur|Un coussin bleu a un gros bouton.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Derrière, on voit les toits du village.
+narrateur|Ça sent le pain encore chaud.
+maman|Raphaël, tu as vu les toits ?
+enfant-m|Oui, maman. Ils sont gris.
+maman|Ils sont gris, et tout calmes.
+papa|J'ai plié une serviette près de la porte.
+maman|Merci.
+narrateur|Un rayon pâle passe sur le coussin.
+narrateur|Le bouton bleu brille un peu.
+maman|Tu as vu le bouton ?
+enfant-m|Oui. Il est rond.
+narrateur|En ce moment, Raphaël est au tapis.
+narrateur|Le tapis a des ronds verts.
+narrateur|Les cubes en bois sont lisses.
+narrateur|Un cube jaune attend.
+narrateur|Un cube rouge attend aussi.
+enfant-m|Je fais une tour, maman.
+maman|Une grande tour.
+narrateur|Raphaël pose le cube jaune.
+narrateur|Il pose le cube rouge dessus.
+narrateur|Le bois fait un petit toc.
+papa|Tes mains sont avec les cubes ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le salon est un peu sombre.
+narrateur|Raphaël veut plus de lumière.
+narrateur|Il regarde ses mains.
+narrateur|Les mains restent avec les jouets.
+narrateur|Raphaël appelle un adulte.
+enfant-m|Maman, la lumière.
+maman|J'arrive, Raphaël.
+narrateur|Maman vient près du tapis.
+maman|Je m'occupe de la lumière.
+narrateur|Maman allume la lampe.
+narrateur|La pièce est claire.
+narrateur|La tour jaune et rouge brille.
+papa|Tu as appelé un adulte.
+papa|On appelle papa ou maman.
+maman|Bravo, Raphaël.
 maman|Les prises sont pour les adultes.
-narrateur|Fabrice tient les cubes. Les mains sont avec les jouets.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Les mains restent avec les jouets.
+narrateur|Raphaël reprend un cube.
+narrateur|Il construit une tour plus haute.
+enfant-m|La tour est haute.
+papa|Oui. Tes mains sont avec les cubes.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël tient les cubes.
+narrateur|Les mains sont avec les jouets.
+narrateur|Le radiateur fait encore tic tic.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fabrice veut la lumière. Que fait-il ?</t>
+          <t>Raphaël veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Fabrice veut la lumière. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël veut la lumière.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fabrice a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>Raphaël a appelé un adulte. Les mains étaient avec les jouets. Tu as appelé maman ? Oui. Bravo. On appelle papa ou maman. La tour tient encore. Le coussin bleu a toujours son bouton. Ça sent encore le pain.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,10 +1738,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Fabrice a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a appelé un adulte.
+narrateur|Les mains étaient avec les jouets.
+maman|Tu as appelé maman ?
+enfant-m|Oui.
+maman|Bravo.
+papa|On appelle papa ou maman.
+narrateur|La tour tient encore.
+narrateur|Le coussin bleu a toujours son bouton.
+narrateur|Ça sent encore le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Fabrice pousse un cube. La lumière reste allumée.</t>
+          <t>Raphaël pousse un cube. Le bois est lisse. La lumière reste allumée. La tour est finie ? Oui, maman. Bravo. Tu as fait du bon travail. On goûte le pain ? Oui, papa. Les toits du village sont encore gris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,10 +1913,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Fabrice pousse un cube. La lumière reste allumée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pousse un cube.
+narrateur|Le bois est lisse.
+narrateur|La lumière reste allumée.
+maman|La tour est finie ?
+enfant-m|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+papa|On goûte le pain ?
+enfant-m|Oui, papa.
+narrateur|Les toits du village sont encore gris.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a fait une tour. Il a appelé maman. Les mains étaient avec les cubes. Bravo, Raphaël. La lumière est là. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,10 +2088,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël a fait une tour.
+narrateur|Il a appelé maman.
+narrateur|Les mains étaient avec les cubes.
+maman|Bravo, Raphaël.
+papa|La lumière est là.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur du salon fait tic tic tic. Un coussin bleu a un gros bouton. La fenêtre est un peu embuée. Derrière, on voit les toits du village. Ça sent le pain encore chaud. Raphaël, tu as vu les toits ? Oui, maman. Ils sont gris. Ils sont gris, et tout calmes. J'ai plié une serviette près de la porte. Merci. Un rayon pâle passe sur le coussin. Le bouton bleu brille un peu. Tu as vu le bouton ? Oui. Il est rond. En ce moment, Raphaël est au tapis. Le tapis a des ronds verts. Les cubes en bois sont lisses. Un cube jaune attend. Un cube rouge attend aussi. Je fais une tour, maman. Une grande tour. Raphaël pose le cube jaune. Il pose le cube rouge dessus. Le bois fait un petit toc. Tes mains sont avec les cubes ? Oui, papa. Bravo. Le salon est un peu sombre. Raphaël veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Raphaël appelle un adulte. Maman, la lumière. J'arrive, Raphaël. Maman vient près du tapis. Je m'occupe de la lumière. Maman allume la lampe. La pièce est claire. La tour jaune et rouge brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Raphaël. Les prises sont pour les adultes. Les mains restent avec les jouets. Raphaël reprend un cube. Il construit une tour plus haute. La tour est haute. Oui. Tes mains sont avec les cubes. Tu as fait du bon travail. Raphaël tient les cubes. Les mains sont avec les jouets. Le radiateur fait encore tic tic.</t>
+          <t>Le radiateur du salon fait tic tic tic. Un coussin bleu a un gros bouton. La fenêtre est un peu embuée. Derrière, on voit les toits du village. Ça sent le pain encore chaud. Raphaël, tu as vu les toits ? Oui, maman. Ils sont gris. Ils sont gris, et tout calmes. J'ai plié une serviette près de la porte. Merci. Un rayon pâle passe sur le coussin. Le bouton bleu brille un peu. Tu as vu le bouton ? Oui. Il est rond. En ce moment, Raphaël est au tapis. Le tapis a des ronds verts. Les cubes en bois sont lisses. Un cube jaune attend. Un cube rouge attend aussi. Je fais une tour, maman. Une grande tour. Raphaël pose le cube jaune. Il pose le cube rouge dessus. Le bois fait un petit toc. Tes mains sont avec les cubes ? Oui, papa. Bravo. Le salon est un peu sombre. Raphaël veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Raphaël appelle un adulte. Maman, la lumière. J'arrive, Raphaël. Maman vient près du tapis. Je m'occupe de la lumière. Maman allume la lampe. La pièce est claire. La tour jaune et rouge brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Raphaël. Les prises sont pour les adultes. Les mains restent avec les jouets. Raphaël reprend un cube. Il construit une tour plus haute. La tour est haute. Oui. Tes mains sont avec les cubes. Raphaël tient les cubes. Les mains sont avec les jouets. Le radiateur fait encore tic tic.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Fabrice joue dans le salon. Il a des cubes en bois. Le bois est lisse. Maman plie une serviette près de la porte. Fabrice veut plus de lumière. Il regarde ses &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt;. Les mains restent avec les jouets. Fabrice appelle un adulte. Il dit : maman, la lumière. Maman vient. Maman allume la lampe. La pièce est claire. Papa entre. Papa dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Fabrice reprend un cube. Il construit une tour. Maman dit : les prises sont pour les adultes. Fabrice tient les cubes. Les mains sont avec les jouets.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le radiateur du salon fait tic tic tic. Un coussin bleu a un gros bouton. La fenêtre est un peu embuée. Derrière, on voit les toits du village. Ça sent le pain encore chaud. Raphaël, tu as vu les toits ? Oui, maman. Ils sont gris. Ils sont gris, et tout calmes. J'ai plié une serviette près de la porte. Merci. Un rayon pâle passe sur le coussin. Le bouton bleu brille un peu. Tu as vu le bouton ? Oui. Il est rond. En ce moment, Raphaël est au tapis. Le tapis a des ronds verts. Les cubes en bois sont lisses. Un cube jaune attend. Un cube rouge attend aussi. Je fais une tour, maman. Une grande tour. Raphaël pose le cube jaune. Il pose le cube rouge dessus. Le bois fait un petit toc. Tes mains sont avec les cubes ? Oui, papa. Bravo. Le salon est un peu sombre. Raphaël veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Raphaël appelle un adulte. Maman, la lumière. J'arrive, Raphaël. Maman vient près du tapis. Je m'occupe de la lumière. Maman allume la lampe. La pièce est claire. La tour jaune et rouge brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Raphaël. Les prises sont pour les adultes. Les mains restent avec les jouets. Raphaël reprend un cube. Il construit une tour plus haute. La tour est haute. Oui. Tes mains sont avec les cubes. Raphaël tient les cubes. Les mains sont avec les jouets. Le radiateur fait encore tic tic.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1372,7 +1372,6 @@
 narrateur|Il construit une tour plus haute.
 enfant-m|La tour est haute.
 papa|Oui. Tes mains sont avec les cubes.
-maman|Tu as fait du bon travail.
 narrateur|Raphaël tient les cubes.
 narrateur|Les mains sont avec les jouets.
 narrateur|Le radiateur fait encore tic tic.</t>
@@ -1407,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Fabrice veut la lumière. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Fabrice a appelé un adulte. Les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; étaient avec les jouets. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a appelé un adulte. Les mains étaient avec les jouets. Tu as appelé maman ? Oui. Bravo. On appelle papa ou maman. La tour tient encore. Le coussin bleu a toujours son bouton. Ça sent encore le pain.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1773,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pousse un cube. Le bois est lisse. La lumière reste allumée. La tour est finie ? Oui, maman. Bravo. Tu as fait du bon travail. On goûte le pain ? Oui, papa. Les toits du village sont encore gris.</t>
+          <t>Raphaël pousse un cube. Le bois est lisse. La lumière reste allumée. La tour est finie ? Oui, maman. On goûte le pain ? Oui, papa. Les toits du village sont encore gris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Fabrice pousse un cube. La lumière reste allumée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pousse un cube. Le bois est lisse. La lumière reste allumée. La tour est finie ? Oui, maman. On goûte le pain ? Oui, papa. Les toits du village sont encore gris.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,7 +1917,6 @@
 narrateur|La lumière reste allumée.
 maman|La tour est finie ?
 enfant-m|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
 papa|On goûte le pain ?
 enfant-m|Oui, papa.
 narrateur|Les toits du village sont encore gris.</t>
@@ -1948,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a fait une tour. Il a appelé maman. Les mains étaient avec les cubes. Bravo, Raphaël. La lumière est là. L'histoire est finie.</t>
+          <t>Raphaël a fait une tour. Il a appelé maman. Les mains étaient avec les cubes. Bravo, Raphaël. La lumière est là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a fait une tour. Il a appelé maman. Les mains étaient avec les cubes. Bravo, Raphaël. La lumière est là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,8 +2090,7 @@
 narrateur|Il a appelé maman.
 narrateur|Les mains étaient avec les cubes.
 maman|Bravo, Raphaël.
-papa|La lumière est là.
-narrateur|L'histoire est finie.</t>
+papa|La lumière est là.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fabrice, maman, papa</t>
+          <t>Raphaël, maman, papa</t>
         </is>
       </c>
     </row>
